--- a/tests/testdata/excel/セル内容.xlsx
+++ b/tests/testdata/excel/セル内容.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{030E594D-8FAA-4E9B-833F-0EA8829E5728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A1FA315-750A-46DE-AA6B-5FF086E5CAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{64AA5EF7-1D45-4E8C-AEA2-3EBBBCE3A107}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{CA77B56D-B782-4530-8C7F-106C1B4CC0B1}"/>
   </bookViews>
   <sheets>
     <sheet name="文字列" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
     <author>test</author>
   </authors>
   <commentList>
-    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{AAC8AD33-D3F9-4BCC-ADA5-EA2A3D691ED3}">
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{18AB48DE-22F7-47B9-B977-DF9B0AF5BED7}">
       <text>
         <r>
           <rPr>
@@ -1870,7 +1870,7 @@
         <xdr:cNvPr id="2" name="テキスト ボックス 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3A44CE5-64DB-6E5A-C9C5-BAD2718E2DD2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E98D655-6DEC-7D82-6379-4740B8DFEB4A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2245,7 +2245,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005539A-1476-451A-B755-A8D3A5259988}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2554C1FB-9129-47D4-A24D-2BDE2B2A777D}">
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -2614,7 +2614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB4E408E-CA53-489B-9FEE-6D93030103AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22452A0D-4C36-4B3D-BC4D-7E6CCB69EA2F}">
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
@@ -2943,7 +2943,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE83B843-2603-415A-8652-9D2A740C5E9C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DA1168-E24A-4404-9F8E-4579A5EF6D31}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -3164,7 +3164,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B5F3E35-13F4-427A-B0CB-34AF62764F5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A49980D-CFE4-4F36-A3D9-735B82CA5A78}">
   <sheetPr filterMode="1"/>
   <dimension ref="A2:KN300"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -4165,7 +4165,7 @@
       <c r="AZ300" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A11:C15" xr:uid="{7B5F3E35-13F4-427A-B0CB-34AF62764F5B}">
+  <autoFilter ref="A11:C15" xr:uid="{9A49980D-CFE4-4F36-A3D9-735B82CA5A78}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter operator="notEqual" val="絞込"/>
@@ -4181,7 +4181,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8B3E618-E188-43C6-895D-A53377230622}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D58D1BE-B045-438B-8436-F232A504E93A}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -4243,12 +4243,12 @@
   </sheetData>
   <phoneticPr fontId="3"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{E6794C3B-E95F-4F8C-94B0-176D840A7DCF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{DD6D5A1C-F060-4648-917C-0A811F902FD6}">
       <formula1>"選択肢A,選択肢B"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{89E6C8E4-D8CE-4FF7-80AC-F2DB25CF3649}"/>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{D5403462-13A4-4AD1-B20C-F33BE8D6364A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>

--- a/tests/testdata/excel/セル内容.xlsx
+++ b/tests/testdata/excel/セル内容.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A1FA315-750A-46DE-AA6B-5FF086E5CAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{383E9E34-A6EF-4368-B36F-C9167B5AAF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{CA77B56D-B782-4530-8C7F-106C1B4CC0B1}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{B5C7F786-6C59-4DF6-8080-97E78632DF74}"/>
   </bookViews>
   <sheets>
     <sheet name="文字列" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
     <author>test</author>
   </authors>
   <commentList>
-    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{18AB48DE-22F7-47B9-B977-DF9B0AF5BED7}">
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{29A023E2-D41B-4238-BFED-4F30552AA9A5}">
       <text>
         <r>
           <rPr>
@@ -1870,7 +1870,7 @@
         <xdr:cNvPr id="2" name="テキスト ボックス 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E98D655-6DEC-7D82-6379-4740B8DFEB4A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45A5D5A7-FD54-32CF-75F2-6A1FEE50A591}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2245,7 +2245,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2554C1FB-9129-47D4-A24D-2BDE2B2A777D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6F58BD-D368-47B8-AA13-EFB87B9DAB95}">
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -2614,7 +2614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22452A0D-4C36-4B3D-BC4D-7E6CCB69EA2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8780B09E-9DFF-4BBB-B552-85B3F5F8E309}">
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
@@ -2943,7 +2943,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DA1168-E24A-4404-9F8E-4579A5EF6D31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C900163-5EF0-4113-ACAF-039E91557202}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -3164,7 +3164,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A49980D-CFE4-4F36-A3D9-735B82CA5A78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2704FBFB-1D93-48DF-8A65-60B43D5A9558}">
   <sheetPr filterMode="1"/>
   <dimension ref="A2:KN300"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -4165,7 +4165,7 @@
       <c r="AZ300" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A11:C15" xr:uid="{9A49980D-CFE4-4F36-A3D9-735B82CA5A78}">
+  <autoFilter ref="A11:C15" xr:uid="{2704FBFB-1D93-48DF-8A65-60B43D5A9558}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter operator="notEqual" val="絞込"/>
@@ -4181,7 +4181,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D58D1BE-B045-438B-8436-F232A504E93A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5998EB62-9C9B-4580-ADE3-6FD3B552D71B}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -4243,12 +4243,12 @@
   </sheetData>
   <phoneticPr fontId="3"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{DD6D5A1C-F060-4648-917C-0A811F902FD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{557F3955-79D0-47B7-8CB3-B0F08EF1FD6B}">
       <formula1>"選択肢A,選択肢B"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{D5403462-13A4-4AD1-B20C-F33BE8D6364A}"/>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{51997399-1A61-41E0-B09F-3C3A474DEBDC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
